--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-bundle-medikationsplantx.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1001,6 +1001,9 @@
   <si>
     <t xml:space="preserve">MedicationRequest {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationrequest-planeintrag}
 </t>
+  </si>
+  <si>
+    <t>Planeintrag</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -11250,10 +11253,10 @@
         <v>312</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11322,7 +11325,7 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>21</v>
@@ -11333,7 +11336,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>195</v>
@@ -11445,7 +11448,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>199</v>
@@ -11557,7 +11560,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>200</v>
@@ -11671,7 +11674,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>201</v>
@@ -11787,7 +11790,7 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>202</v>
@@ -11901,7 +11904,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>208</v>
@@ -12015,7 +12018,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>213</v>
@@ -12127,7 +12130,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>217</v>
@@ -12239,7 +12242,7 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>218</v>
@@ -12353,7 +12356,7 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>219</v>
@@ -12469,7 +12472,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>220</v>
@@ -12581,7 +12584,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>225</v>
@@ -12695,7 +12698,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>229</v>
@@ -12807,7 +12810,7 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>232</v>
@@ -12919,7 +12922,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>234</v>
@@ -13031,7 +13034,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>237</v>
@@ -13143,7 +13146,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>240</v>
@@ -13255,7 +13258,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>244</v>
@@ -13367,7 +13370,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>245</v>
@@ -13481,7 +13484,7 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>246</v>
@@ -13597,7 +13600,7 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>247</v>
@@ -13709,7 +13712,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>250</v>
@@ -13821,7 +13824,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>253</v>
@@ -13935,7 +13938,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>257</v>
@@ -14049,7 +14052,7 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>261</v>
@@ -14163,10 +14166,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14189,19 +14192,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
@@ -14250,7 +14253,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
